--- a/Literature-review/data/data_extraction.xlsx
+++ b/Literature-review/data/data_extraction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enric\Desktop\Paper Taxometrics Neurodevelopmental\Articles included in review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D814CB6A-C49E-4885-80BE-66340D82696D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63CBA53B-E804-4B5A-9E10-0AB9955342A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="235">
   <si>
     <t>ID_article</t>
   </si>
@@ -724,6 +724,12 @@
   </si>
   <si>
     <t>[defined by NDW: SLI:0.00;LN:-0.14; defined by 3-4 PPC: SLI:0.06;LN:0.11]</t>
+  </si>
+  <si>
+    <t>mean=0.14; range=-0.03 to 0.23</t>
+  </si>
+  <si>
+    <t>mean=0.15; range=0.04 to 0.22</t>
   </si>
 </sst>
 </file>
@@ -2402,7 +2408,9 @@
       <c r="Q14" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="R14" s="8"/>
+      <c r="R14" s="8" t="s">
+        <v>233</v>
+      </c>
       <c r="S14" s="8" t="s">
         <v>58</v>
       </c>
@@ -2471,7 +2479,9 @@
       <c r="Q15" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="R15" s="13"/>
+      <c r="R15" s="13" t="s">
+        <v>234</v>
+      </c>
       <c r="S15" s="13" t="s">
         <v>62</v>
       </c>
@@ -2540,7 +2550,9 @@
       <c r="Q16" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="R16" s="16"/>
+      <c r="R16" s="16">
+        <v>0.27</v>
+      </c>
       <c r="S16" s="16">
         <v>2.33</v>
       </c>
@@ -2611,7 +2623,9 @@
       <c r="Q17" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="R17" s="21"/>
+      <c r="R17" s="21">
+        <v>0.27</v>
+      </c>
       <c r="S17" s="21">
         <v>1.23</v>
       </c>
@@ -2680,7 +2694,9 @@
       <c r="Q18" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="R18" s="30"/>
+      <c r="R18" s="30">
+        <v>0.24</v>
+      </c>
       <c r="S18" s="30">
         <v>3.69</v>
       </c>
@@ -2749,7 +2765,9 @@
       <c r="Q19" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="R19" s="30"/>
+      <c r="R19" s="30">
+        <v>0.09</v>
+      </c>
       <c r="S19" s="30">
         <v>3.09</v>
       </c>
@@ -2818,7 +2836,9 @@
       <c r="Q20" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="R20" s="30"/>
+      <c r="R20" s="30">
+        <v>0.11</v>
+      </c>
       <c r="S20" s="30">
         <v>2.13</v>
       </c>
@@ -2887,7 +2907,9 @@
       <c r="Q21" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="R21" s="30"/>
+      <c r="R21" s="30">
+        <v>0.25</v>
+      </c>
       <c r="S21" s="30">
         <v>1.03</v>
       </c>
@@ -2956,7 +2978,9 @@
       <c r="Q22" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="R22" s="30"/>
+      <c r="R22" s="30">
+        <v>0.04</v>
+      </c>
       <c r="S22" s="30">
         <v>2.23</v>
       </c>
@@ -3025,7 +3049,9 @@
       <c r="Q23" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="R23" s="30"/>
+      <c r="R23" s="30">
+        <v>0.15</v>
+      </c>
       <c r="S23" s="30">
         <v>1.28</v>
       </c>
@@ -3094,7 +3120,9 @@
       <c r="Q24" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="R24" s="30"/>
+      <c r="R24" s="30">
+        <v>-0.14000000000000001</v>
+      </c>
       <c r="S24" s="30">
         <v>1.95</v>
       </c>
@@ -3163,7 +3191,9 @@
       <c r="Q25" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="R25" s="30"/>
+      <c r="R25" s="30">
+        <v>0.08</v>
+      </c>
       <c r="S25" s="30">
         <v>1.17</v>
       </c>
@@ -3232,7 +3262,9 @@
       <c r="Q26" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="R26" s="30"/>
+      <c r="R26" s="30">
+        <v>0.24</v>
+      </c>
       <c r="S26" s="30">
         <v>2.3199999999999998</v>
       </c>
@@ -3301,7 +3333,9 @@
       <c r="Q27" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="R27" s="30"/>
+      <c r="R27" s="30">
+        <v>0.21</v>
+      </c>
       <c r="S27" s="30">
         <v>1.47</v>
       </c>
@@ -3370,7 +3404,9 @@
       <c r="Q28" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="R28" s="30"/>
+      <c r="R28" s="30">
+        <v>0.31</v>
+      </c>
       <c r="S28" s="30">
         <v>3.59</v>
       </c>
@@ -3439,7 +3475,9 @@
       <c r="Q29" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="R29" s="30"/>
+      <c r="R29" s="30">
+        <v>0.13</v>
+      </c>
       <c r="S29" s="30">
         <v>2.99</v>
       </c>
@@ -3508,7 +3546,9 @@
       <c r="Q30" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="R30" s="30"/>
+      <c r="R30" s="30">
+        <v>0.13</v>
+      </c>
       <c r="S30" s="30">
         <v>1.82</v>
       </c>
@@ -3577,7 +3617,9 @@
       <c r="Q31" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="R31" s="30"/>
+      <c r="R31" s="30">
+        <v>0.25</v>
+      </c>
       <c r="S31" s="30">
         <v>1.32</v>
       </c>
@@ -3646,7 +3688,9 @@
       <c r="Q32" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="R32" s="30"/>
+      <c r="R32" s="30">
+        <v>0.03</v>
+      </c>
       <c r="S32" s="30">
         <v>1.91</v>
       </c>
@@ -3715,7 +3759,9 @@
       <c r="Q33" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="R33" s="30"/>
+      <c r="R33" s="30">
+        <v>0.14000000000000001</v>
+      </c>
       <c r="S33" s="30">
         <v>1.27</v>
       </c>
@@ -3784,7 +3830,9 @@
       <c r="Q34" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="R34" s="30"/>
+      <c r="R34" s="30">
+        <v>-0.21</v>
+      </c>
       <c r="S34" s="30">
         <v>1.92</v>
       </c>
@@ -3853,7 +3901,9 @@
       <c r="Q35" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="R35" s="30"/>
+      <c r="R35" s="30">
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="S35" s="30">
         <v>1.1200000000000001</v>
       </c>
@@ -3922,7 +3972,9 @@
       <c r="Q36" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="R36" s="30"/>
+      <c r="R36" s="30">
+        <v>0.09</v>
+      </c>
       <c r="S36" s="30">
         <v>2.97</v>
       </c>
@@ -3991,7 +4043,9 @@
       <c r="Q37" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="R37" s="30"/>
+      <c r="R37" s="30">
+        <v>0.21</v>
+      </c>
       <c r="S37" s="30">
         <v>1.1100000000000001</v>
       </c>
@@ -4060,7 +4114,9 @@
         <v>93</v>
       </c>
       <c r="Q38" s="8"/>
-      <c r="R38" s="8"/>
+      <c r="R38" s="8">
+        <v>0.35</v>
+      </c>
       <c r="S38" s="8">
         <v>2.65</v>
       </c>
@@ -4127,7 +4183,9 @@
         <v>95</v>
       </c>
       <c r="Q39" s="13"/>
-      <c r="R39" s="13"/>
+      <c r="R39" s="13">
+        <v>0.23</v>
+      </c>
       <c r="S39" s="13">
         <v>2.3199999999999998</v>
       </c>
@@ -4190,7 +4248,9 @@
         <v>96</v>
       </c>
       <c r="Q40" s="8"/>
-      <c r="R40" s="8"/>
+      <c r="R40" s="8">
+        <v>0.3</v>
+      </c>
       <c r="S40" s="8">
         <v>2.83</v>
       </c>
@@ -4255,7 +4315,9 @@
         <v>97</v>
       </c>
       <c r="Q41" s="13"/>
-      <c r="R41" s="13"/>
+      <c r="R41" s="13">
+        <v>0.04</v>
+      </c>
       <c r="S41" s="13">
         <v>1.96</v>
       </c>
@@ -4322,7 +4384,9 @@
         <v>99</v>
       </c>
       <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
+      <c r="R42" s="8">
+        <v>0</v>
+      </c>
       <c r="S42" s="8">
         <v>2.02</v>
       </c>
@@ -4389,7 +4453,9 @@
         <v>100</v>
       </c>
       <c r="Q43" s="13"/>
-      <c r="R43" s="13"/>
+      <c r="R43" s="13">
+        <v>0.27</v>
+      </c>
       <c r="S43" s="13">
         <v>2.4700000000000002</v>
       </c>
@@ -4454,7 +4520,9 @@
         <v>101</v>
       </c>
       <c r="Q44" s="8"/>
-      <c r="R44" s="8"/>
+      <c r="R44" s="8">
+        <v>0.15</v>
+      </c>
       <c r="S44" s="8">
         <v>1.96</v>
       </c>
@@ -4517,7 +4585,9 @@
         <v>102</v>
       </c>
       <c r="Q45" s="13"/>
-      <c r="R45" s="13"/>
+      <c r="R45" s="13">
+        <v>0.28999999999999998</v>
+      </c>
       <c r="S45" s="13">
         <v>2.92</v>
       </c>
@@ -4582,7 +4652,9 @@
         <v>103</v>
       </c>
       <c r="Q46" s="8"/>
-      <c r="R46" s="8"/>
+      <c r="R46" s="8">
+        <v>-0.12</v>
+      </c>
       <c r="S46" s="8">
         <v>2.39</v>
       </c>
@@ -4649,7 +4721,9 @@
         <v>0.37</v>
       </c>
       <c r="Q47" s="13"/>
-      <c r="R47" s="13"/>
+      <c r="R47" s="13">
+        <v>0.2</v>
+      </c>
       <c r="S47" s="13">
         <v>3.06</v>
       </c>
@@ -4714,7 +4788,9 @@
         <v>0.41299999999999998</v>
       </c>
       <c r="Q48" s="8"/>
-      <c r="R48" s="8"/>
+      <c r="R48" s="8">
+        <v>0.28999999999999998</v>
+      </c>
       <c r="S48" s="8">
         <v>3</v>
       </c>
@@ -4777,7 +4853,9 @@
         <v>0.311</v>
       </c>
       <c r="Q49" s="13"/>
-      <c r="R49" s="13"/>
+      <c r="R49" s="13">
+        <v>0.17</v>
+      </c>
       <c r="S49" s="13">
         <v>3.26</v>
       </c>
@@ -4842,7 +4920,9 @@
         <v>105</v>
       </c>
       <c r="Q50" s="8"/>
-      <c r="R50" s="8"/>
+      <c r="R50" s="8">
+        <v>0.08</v>
+      </c>
       <c r="S50" s="8">
         <v>2.62</v>
       </c>
@@ -4909,7 +4989,9 @@
         <v>106</v>
       </c>
       <c r="Q51" s="13"/>
-      <c r="R51" s="13"/>
+      <c r="R51" s="13">
+        <v>0.06</v>
+      </c>
       <c r="S51" s="13">
         <v>1.87</v>
       </c>
@@ -4976,7 +5058,9 @@
         <v>107</v>
       </c>
       <c r="Q52" s="8"/>
-      <c r="R52" s="8"/>
+      <c r="R52" s="8">
+        <v>0.04</v>
+      </c>
       <c r="S52" s="8">
         <v>2.1</v>
       </c>

--- a/Literature-review/data/data_extraction.xlsx
+++ b/Literature-review/data/data_extraction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enric\Desktop\Paper Taxometrics Neurodevelopmental\Articles included in review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63CBA53B-E804-4B5A-9E10-0AB9955342A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E731A209-593A-4212-BAE3-0F5F872D210C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -487,20 +487,12 @@
     <t>MAMBAC;MAXCOV;MAXEIG;L-Mode</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27; 0.72; -0.48; 0.53; 0.73; -0.02; 0.29;0.67
-</t>
-  </si>
-  <si>
     <t>0.862;0.669;0.68;0.775</t>
   </si>
   <si>
     <t>[Taxon: 0.12;-0.09;0.23;0.22;0.10;0.18; Complement: 0.28;0.13;0.24;0.24;0.10;0.14]</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99;2.21;1.17;2.10;1.09;1.47;0.15;1.02
-</t>
-  </si>
-  <si>
     <t>strong</t>
   </si>
   <si>
@@ -730,6 +722,12 @@
   </si>
   <si>
     <t>mean=0.15; range=0.04 to 0.22</t>
+  </si>
+  <si>
+    <t>0.42;0.73;-0.33;0.02</t>
+  </si>
+  <si>
+    <t>2.33;2.18;1.29;1.47</t>
   </si>
 </sst>
 </file>
@@ -1500,7 +1498,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>11</v>
@@ -1527,7 +1525,7 @@
         <v>18</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="V1" s="5" t="s">
         <v>19</v>
@@ -1536,13 +1534,13 @@
         <v>20</v>
       </c>
       <c r="X1" s="58" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y1" s="58" t="s">
+        <v>223</v>
+      </c>
+      <c r="Z1" s="58" t="s">
         <v>224</v>
-      </c>
-      <c r="Y1" s="58" t="s">
-        <v>225</v>
-      </c>
-      <c r="Z1" s="58" t="s">
-        <v>226</v>
       </c>
       <c r="AA1" s="58"/>
     </row>
@@ -1608,16 +1606,16 @@
         <v>29</v>
       </c>
       <c r="W2" s="59" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="X2" s="59" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Y2" s="59" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Z2" s="59" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AA2" s="59"/>
     </row>
@@ -1684,13 +1682,13 @@
       </c>
       <c r="W3" s="59"/>
       <c r="X3" s="59" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Y3" s="59" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Z3" s="59" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AA3" s="59"/>
     </row>
@@ -1757,10 +1755,10 @@
       </c>
       <c r="W4" s="59"/>
       <c r="X4" s="59" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Y4" s="59" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Z4" s="59"/>
       <c r="AA4" s="59"/>
@@ -1826,10 +1824,10 @@
       <c r="V5" s="10"/>
       <c r="W5" s="59"/>
       <c r="X5" s="59" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Y5" s="59" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Z5" s="59"/>
       <c r="AA5" s="59"/>
@@ -1893,10 +1891,10 @@
       </c>
       <c r="W6" s="59"/>
       <c r="X6" s="59" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Y6" s="59" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Z6" s="59"/>
       <c r="AA6" s="59"/>
@@ -1960,10 +1958,10 @@
       </c>
       <c r="W7" s="59"/>
       <c r="X7" s="59" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Y7" s="59" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Z7" s="59"/>
       <c r="AA7" s="59"/>
@@ -2409,7 +2407,7 @@
         <v>57</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="S14" s="8" t="s">
         <v>58</v>
@@ -2480,7 +2478,7 @@
         <v>61</v>
       </c>
       <c r="R15" s="13" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="S15" s="13" t="s">
         <v>62</v>
@@ -2526,7 +2524,7 @@
         <v>40</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J16" s="16">
         <v>315</v>
@@ -2565,7 +2563,7 @@
       <c r="V16" s="18"/>
       <c r="W16" s="60"/>
       <c r="X16" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y16" s="60" t="s">
         <v>68</v>
@@ -2599,7 +2597,7 @@
         <v>40</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J17" s="21">
         <v>342</v>
@@ -2638,7 +2636,7 @@
       <c r="V17" s="18"/>
       <c r="W17" s="60"/>
       <c r="X17" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y17" s="60"/>
       <c r="Z17" s="60"/>
@@ -2670,7 +2668,7 @@
         <v>40</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J18" s="30">
         <v>338</v>
@@ -2709,7 +2707,7 @@
       <c r="V18" s="31"/>
       <c r="W18" s="60"/>
       <c r="X18" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y18" s="60"/>
       <c r="Z18" s="60"/>
@@ -2741,7 +2739,7 @@
         <v>40</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J19" s="30">
         <v>338</v>
@@ -2780,7 +2778,7 @@
       <c r="V19" s="31"/>
       <c r="W19" s="60"/>
       <c r="X19" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y19" s="60"/>
       <c r="Z19" s="60"/>
@@ -2812,7 +2810,7 @@
         <v>40</v>
       </c>
       <c r="I20" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J20" s="30">
         <v>384</v>
@@ -2851,7 +2849,7 @@
       <c r="V20" s="31"/>
       <c r="W20" s="60"/>
       <c r="X20" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y20" s="60"/>
       <c r="Z20" s="60"/>
@@ -2883,7 +2881,7 @@
         <v>40</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J21" s="30">
         <v>384</v>
@@ -2922,7 +2920,7 @@
       <c r="V21" s="31"/>
       <c r="W21" s="60"/>
       <c r="X21" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y21" s="60"/>
       <c r="Z21" s="60"/>
@@ -2954,7 +2952,7 @@
         <v>40</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J22" s="30">
         <v>394</v>
@@ -2993,7 +2991,7 @@
       <c r="V22" s="31"/>
       <c r="W22" s="60"/>
       <c r="X22" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y22" s="60"/>
       <c r="Z22" s="60"/>
@@ -3025,7 +3023,7 @@
         <v>40</v>
       </c>
       <c r="I23" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J23" s="30">
         <v>390</v>
@@ -3064,7 +3062,7 @@
       <c r="V23" s="31"/>
       <c r="W23" s="60"/>
       <c r="X23" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y23" s="60"/>
       <c r="Z23" s="60"/>
@@ -3096,7 +3094,7 @@
         <v>40</v>
       </c>
       <c r="I24" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J24" s="30">
         <v>347</v>
@@ -3135,7 +3133,7 @@
       <c r="V24" s="31"/>
       <c r="W24" s="60"/>
       <c r="X24" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y24" s="60"/>
       <c r="Z24" s="60"/>
@@ -3167,7 +3165,7 @@
         <v>40</v>
       </c>
       <c r="I25" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J25" s="30">
         <v>244</v>
@@ -3206,7 +3204,7 @@
       <c r="V25" s="31"/>
       <c r="W25" s="60"/>
       <c r="X25" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y25" s="60"/>
       <c r="Z25" s="60"/>
@@ -3238,7 +3236,7 @@
         <v>40</v>
       </c>
       <c r="I26" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J26" s="30">
         <v>245</v>
@@ -3277,7 +3275,7 @@
       <c r="V26" s="31"/>
       <c r="W26" s="60"/>
       <c r="X26" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y26" s="60"/>
       <c r="Z26" s="60"/>
@@ -3309,7 +3307,7 @@
         <v>40</v>
       </c>
       <c r="I27" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J27" s="30">
         <v>270</v>
@@ -3348,7 +3346,7 @@
       <c r="V27" s="31"/>
       <c r="W27" s="60"/>
       <c r="X27" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y27" s="60"/>
       <c r="Z27" s="60"/>
@@ -3380,7 +3378,7 @@
         <v>40</v>
       </c>
       <c r="I28" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J28" s="30">
         <v>266</v>
@@ -3419,7 +3417,7 @@
       <c r="V28" s="31"/>
       <c r="W28" s="60"/>
       <c r="X28" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y28" s="60"/>
       <c r="Z28" s="60"/>
@@ -3451,7 +3449,7 @@
         <v>40</v>
       </c>
       <c r="I29" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J29" s="30">
         <v>266</v>
@@ -3490,7 +3488,7 @@
       <c r="V29" s="31"/>
       <c r="W29" s="60"/>
       <c r="X29" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y29" s="60"/>
       <c r="Z29" s="60"/>
@@ -3522,7 +3520,7 @@
         <v>40</v>
       </c>
       <c r="I30" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J30" s="30">
         <v>308</v>
@@ -3561,7 +3559,7 @@
       <c r="V30" s="31"/>
       <c r="W30" s="60"/>
       <c r="X30" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y30" s="60"/>
       <c r="Z30" s="60"/>
@@ -3593,7 +3591,7 @@
         <v>40</v>
       </c>
       <c r="I31" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J31" s="30">
         <v>308</v>
@@ -3632,7 +3630,7 @@
       <c r="V31" s="31"/>
       <c r="W31" s="60"/>
       <c r="X31" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y31" s="60"/>
       <c r="Z31" s="60"/>
@@ -3664,7 +3662,7 @@
         <v>40</v>
       </c>
       <c r="I32" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J32" s="30">
         <v>317</v>
@@ -3703,7 +3701,7 @@
       <c r="V32" s="31"/>
       <c r="W32" s="60"/>
       <c r="X32" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y32" s="60"/>
       <c r="Z32" s="60"/>
@@ -3735,7 +3733,7 @@
         <v>40</v>
       </c>
       <c r="I33" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J33" s="30">
         <v>313</v>
@@ -3774,7 +3772,7 @@
       <c r="V33" s="31"/>
       <c r="W33" s="60"/>
       <c r="X33" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y33" s="60"/>
       <c r="Z33" s="60"/>
@@ -3806,7 +3804,7 @@
         <v>40</v>
       </c>
       <c r="I34" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J34" s="30">
         <v>278</v>
@@ -3845,7 +3843,7 @@
       <c r="V34" s="31"/>
       <c r="W34" s="60"/>
       <c r="X34" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y34" s="60"/>
       <c r="Z34" s="60"/>
@@ -3877,7 +3875,7 @@
         <v>40</v>
       </c>
       <c r="I35" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J35" s="30">
         <v>191</v>
@@ -3916,7 +3914,7 @@
       <c r="V35" s="31"/>
       <c r="W35" s="60"/>
       <c r="X35" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y35" s="60"/>
       <c r="Z35" s="60"/>
@@ -3987,7 +3985,7 @@
       <c r="V36" s="31"/>
       <c r="W36" s="60"/>
       <c r="X36" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y36" s="60"/>
       <c r="Z36" s="60"/>
@@ -4058,7 +4056,7 @@
       <c r="V37" s="31"/>
       <c r="W37" s="60"/>
       <c r="X37" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y37" s="60"/>
       <c r="Z37" s="60"/>
@@ -5595,7 +5593,7 @@
         <v>130</v>
       </c>
       <c r="X60" s="59" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="Y60" s="59" t="s">
         <v>131</v>
@@ -5664,7 +5662,7 @@
       <c r="V61" s="38"/>
       <c r="W61" s="59"/>
       <c r="X61" s="59" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="Y61" s="59" t="s">
         <v>133</v>
@@ -5733,7 +5731,7 @@
       <c r="V62" s="38"/>
       <c r="W62" s="59"/>
       <c r="X62" s="59" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="Y62" s="59" t="s">
         <v>135</v>
@@ -5802,7 +5800,7 @@
       <c r="V63" s="38"/>
       <c r="W63" s="59"/>
       <c r="X63" s="59" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="Y63" s="59" t="s">
         <v>137</v>
@@ -6233,36 +6231,36 @@
         <v>153</v>
       </c>
       <c r="N70" s="8">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O70" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="P70" s="8" t="s">
         <v>154</v>
-      </c>
-      <c r="P70" s="8" t="s">
-        <v>155</v>
       </c>
       <c r="Q70" s="8"/>
       <c r="R70" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="S70" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="T70" s="8">
+        <v>1</v>
+      </c>
+      <c r="U70" s="9">
+        <v>1</v>
+      </c>
+      <c r="V70" s="10" t="s">
         <v>156</v>
-      </c>
-      <c r="S70" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="T70" s="8">
-        <v>1</v>
-      </c>
-      <c r="U70" s="9">
-        <v>1</v>
-      </c>
-      <c r="V70" s="10" t="s">
-        <v>158</v>
       </c>
       <c r="W70" s="59"/>
       <c r="X70" s="59" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="Y70" s="59" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="Z70" s="59"/>
       <c r="AA70" s="59"/>
@@ -6278,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E71" s="27" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F71" s="27">
         <v>2008</v>
       </c>
       <c r="G71" s="27" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H71" s="21" t="s">
         <v>111</v>
@@ -6305,7 +6303,7 @@
         <v>0</v>
       </c>
       <c r="M71" s="21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N71" s="21">
         <v>4</v>
@@ -6323,13 +6321,13 @@
       </c>
       <c r="V71" s="18"/>
       <c r="W71" s="60" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="X71" s="60" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="Y71" s="60" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="Z71" s="60"/>
       <c r="AA71" s="60"/>
@@ -6345,16 +6343,16 @@
         <v>0</v>
       </c>
       <c r="D72" s="36" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E72" s="36" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F72" s="36">
         <v>2018</v>
       </c>
       <c r="G72" s="36" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H72" s="8" t="s">
         <v>40</v>
@@ -6372,14 +6370,14 @@
         <v>1</v>
       </c>
       <c r="M72" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N72" s="8">
         <v>3</v>
       </c>
       <c r="O72" s="8"/>
       <c r="P72" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="Q72" s="8"/>
       <c r="R72" s="8"/>
@@ -6393,7 +6391,7 @@
       <c r="V72" s="10"/>
       <c r="W72" s="59"/>
       <c r="X72" s="59" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Y72" s="59"/>
       <c r="Z72" s="59"/>
@@ -6410,16 +6408,16 @@
         <v>1</v>
       </c>
       <c r="D73" s="41" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E73" s="41" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F73" s="41">
         <v>2018</v>
       </c>
       <c r="G73" s="41" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H73" s="13" t="s">
         <v>40</v>
@@ -6435,14 +6433,14 @@
       </c>
       <c r="L73" s="13"/>
       <c r="M73" s="13" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N73" s="13">
         <v>3</v>
       </c>
       <c r="O73" s="13"/>
       <c r="P73" s="13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q73" s="13"/>
       <c r="R73" s="13"/>
@@ -6469,16 +6467,16 @@
         <v>0</v>
       </c>
       <c r="D74" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E74" s="24" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F74" s="24">
         <v>2023</v>
       </c>
       <c r="G74" s="24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H74" s="16" t="s">
         <v>111</v>
@@ -6505,11 +6503,11 @@
         <v>0.26</v>
       </c>
       <c r="P74" s="16" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q74" s="44"/>
       <c r="R74" s="16" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="S74" s="16">
         <v>0.85</v>
@@ -6523,7 +6521,7 @@
       <c r="V74" s="18"/>
       <c r="W74" s="60"/>
       <c r="X74" s="60" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="Y74" s="60"/>
       <c r="Z74" s="60"/>
@@ -6540,16 +6538,16 @@
         <v>0</v>
       </c>
       <c r="D75" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E75" s="27" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F75" s="27">
         <v>2023</v>
       </c>
       <c r="G75" s="27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H75" s="21" t="s">
         <v>111</v>
@@ -6576,11 +6574,11 @@
         <v>0.23</v>
       </c>
       <c r="P75" s="21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q75" s="44"/>
       <c r="R75" s="21" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S75" s="21">
         <v>1.29</v>
@@ -6594,7 +6592,7 @@
       <c r="V75" s="18"/>
       <c r="W75" s="60"/>
       <c r="X75" s="60" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="Y75" s="60"/>
       <c r="Z75" s="60"/>
@@ -6611,16 +6609,16 @@
         <v>0</v>
       </c>
       <c r="D76" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E76" s="27" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F76" s="27">
         <v>2023</v>
       </c>
       <c r="G76" s="27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H76" s="30" t="s">
         <v>111</v>
@@ -6647,11 +6645,11 @@
         <v>0.48</v>
       </c>
       <c r="P76" s="44" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Q76" s="44"/>
       <c r="R76" s="44" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="S76" s="44">
         <v>0.56999999999999995</v>
@@ -6665,7 +6663,7 @@
       <c r="V76" s="51"/>
       <c r="W76" s="60"/>
       <c r="X76" s="60" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Y76" s="60"/>
       <c r="Z76" s="60"/>
@@ -6682,16 +6680,16 @@
         <v>0</v>
       </c>
       <c r="D77" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E77" s="27" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F77" s="27">
         <v>2023</v>
       </c>
       <c r="G77" s="27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H77" s="30" t="s">
         <v>111</v>
@@ -6718,11 +6716,11 @@
         <v>0.23</v>
       </c>
       <c r="P77" s="44" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q77" s="44"/>
       <c r="R77" s="44" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S77" s="44">
         <v>1.3</v>
@@ -6736,7 +6734,7 @@
       <c r="V77" s="51"/>
       <c r="W77" s="60"/>
       <c r="X77" s="60" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="Y77" s="60"/>
       <c r="Z77" s="60"/>
@@ -6753,16 +6751,16 @@
         <v>0</v>
       </c>
       <c r="D78" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E78" s="27" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F78" s="27">
         <v>2023</v>
       </c>
       <c r="G78" s="27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H78" s="30" t="s">
         <v>111</v>
@@ -6789,11 +6787,11 @@
         <v>0.31</v>
       </c>
       <c r="P78" s="44" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q78" s="44"/>
       <c r="R78" s="44" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="S78" s="44">
         <v>1.25</v>
@@ -6807,7 +6805,7 @@
       <c r="V78" s="51"/>
       <c r="W78" s="60"/>
       <c r="X78" s="60" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="Y78" s="60"/>
       <c r="Z78" s="60"/>
@@ -6824,16 +6822,16 @@
         <v>0</v>
       </c>
       <c r="D79" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E79" s="27" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F79" s="27">
         <v>2023</v>
       </c>
       <c r="G79" s="27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H79" s="30" t="s">
         <v>111</v>
@@ -6860,11 +6858,11 @@
         <v>0.3</v>
       </c>
       <c r="P79" s="44" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="Q79" s="44"/>
       <c r="R79" s="44" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="S79" s="44">
         <v>1.78</v>
@@ -6878,7 +6876,7 @@
       <c r="V79" s="51"/>
       <c r="W79" s="60"/>
       <c r="X79" s="60" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="Y79" s="60"/>
       <c r="Z79" s="60"/>
@@ -6895,16 +6893,16 @@
         <v>0</v>
       </c>
       <c r="D80" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E80" s="27" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F80" s="27">
         <v>2023</v>
       </c>
       <c r="G80" s="27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H80" s="30" t="s">
         <v>111</v>
@@ -6931,11 +6929,11 @@
         <v>0.19</v>
       </c>
       <c r="P80" s="44" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="Q80" s="44"/>
       <c r="R80" s="44" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="S80" s="44">
         <v>1.84</v>
@@ -6949,7 +6947,7 @@
       <c r="V80" s="51"/>
       <c r="W80" s="60"/>
       <c r="X80" s="60" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="Y80" s="60"/>
       <c r="Z80" s="60"/>
@@ -6966,16 +6964,16 @@
         <v>0</v>
       </c>
       <c r="D81" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E81" s="27" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F81" s="27">
         <v>2023</v>
       </c>
       <c r="G81" s="27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H81" s="30" t="s">
         <v>111</v>
@@ -7002,11 +7000,11 @@
         <v>0.99</v>
       </c>
       <c r="P81" s="44" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="Q81" s="44"/>
       <c r="R81" s="44" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="S81" s="44">
         <v>1.32</v>
@@ -7020,7 +7018,7 @@
       <c r="V81" s="51"/>
       <c r="W81" s="60"/>
       <c r="X81" s="60" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="Y81" s="60"/>
       <c r="Z81" s="60"/>
@@ -7037,16 +7035,16 @@
         <v>0</v>
       </c>
       <c r="D82" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E82" s="27" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F82" s="27">
         <v>2023</v>
       </c>
       <c r="G82" s="27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H82" s="30" t="s">
         <v>111</v>
@@ -7073,11 +7071,11 @@
         <v>0.63</v>
       </c>
       <c r="P82" s="44" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="Q82" s="44"/>
       <c r="R82" s="44" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="S82" s="44">
         <v>1.31</v>
@@ -7091,7 +7089,7 @@
       <c r="V82" s="51"/>
       <c r="W82" s="60"/>
       <c r="X82" s="60" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="Y82" s="60"/>
       <c r="Z82" s="60"/>
@@ -7108,16 +7106,16 @@
         <v>0</v>
       </c>
       <c r="D83" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E83" s="27" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F83" s="27">
         <v>2023</v>
       </c>
       <c r="G83" s="27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H83" s="30" t="s">
         <v>111</v>
@@ -7144,11 +7142,11 @@
         <v>0.75</v>
       </c>
       <c r="P83" s="44" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="Q83" s="44"/>
       <c r="R83" s="44" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S83" s="44">
         <v>0.68</v>
@@ -7179,19 +7177,19 @@
         <v>0</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E84" s="36" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F84" s="36">
         <v>2004</v>
       </c>
       <c r="G84" s="36" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I84" s="8" t="s">
         <v>54</v>
@@ -7215,10 +7213,10 @@
       <c r="P84" s="8"/>
       <c r="Q84" s="8"/>
       <c r="R84" s="8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="S84" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="T84" s="8">
         <v>0</v>
@@ -7228,10 +7226,10 @@
       </c>
       <c r="V84" s="10"/>
       <c r="W84" s="59" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="X84" s="59" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="Y84" s="59"/>
       <c r="Z84" s="59"/>
@@ -7248,19 +7246,19 @@
         <v>0</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E85" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F85" s="41">
         <v>2004</v>
       </c>
       <c r="G85" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H85" s="13" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I85" s="13" t="s">
         <v>54</v>
@@ -7284,10 +7282,10 @@
       <c r="P85" s="13"/>
       <c r="Q85" s="13"/>
       <c r="R85" s="13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="S85" s="13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="T85" s="13">
         <v>0</v>
@@ -7298,7 +7296,7 @@
       <c r="V85" s="10"/>
       <c r="W85" s="59"/>
       <c r="X85" s="59" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="Y85" s="59"/>
       <c r="Z85" s="59"/>
@@ -7315,19 +7313,19 @@
         <v>0</v>
       </c>
       <c r="D86" s="53" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E86" s="54" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F86" s="54">
         <v>2011</v>
       </c>
       <c r="G86" s="54" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H86" s="53" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I86" s="53" t="s">
         <v>54</v>
@@ -7351,10 +7349,10 @@
       <c r="P86" s="53"/>
       <c r="Q86" s="55"/>
       <c r="R86" s="53" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="S86" s="53" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="T86" s="53">
         <v>0</v>
@@ -7365,7 +7363,7 @@
       <c r="V86" s="18"/>
       <c r="W86" s="60"/>
       <c r="X86" s="60" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="Y86" s="60"/>
       <c r="Z86" s="60"/>
